--- a/doc/samples/1835154375产品模板.xlsx
+++ b/doc/samples/1835154375产品模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\menghl2\WorkSpace\Projects\Tools\AutoScrew\doc\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70811452-BC38-4F0D-881C-3614A18CBCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9431FB-DED5-48DE-909C-8C350048671C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>螺钉PN</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,10 @@
   </si>
   <si>
     <t>1830330479-00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1830330479-01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -520,24 +524,56 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1830330479</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1830330479</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
